--- a/mo/frontier_45.xlsx
+++ b/mo/frontier_45.xlsx
@@ -1,43 +1,74 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\exchange\ms_excitonic\mo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="10260"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+  <si>
+    <t>occ</t>
+  </si>
+  <si>
+    <t>symm</t>
+  </si>
+  <si>
+    <t>Au</t>
+  </si>
+  <si>
+    <t>Bg</t>
+  </si>
+  <si>
+    <t>Ag</t>
+  </si>
+  <si>
+    <t>Bu</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,121 +77,47 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -448,364 +405,344 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>occ</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>symm</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Au</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Bg</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Ag</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Au</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Bg</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>Bu</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>0</v>
       </c>
-      <c r="B4" t="n">
-        <v>-6.059975450635</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-6.793594391583</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B4" s="3">
+        <v>-6.0599754506350001</v>
+      </c>
+      <c r="C4" s="3">
+        <v>-6.7935943915830004</v>
+      </c>
+      <c r="D4" s="3">
         <v>-1.253900623104</v>
       </c>
-      <c r="E4" t="n">
-        <v>-1.9077902058555</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" s="3">
+        <v>-1.9077902058555001</v>
+      </c>
+      <c r="F4" s="3">
         <v>-1.253900623104</v>
       </c>
-      <c r="G4" t="n">
-        <v>-1.9077902058555</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="G4" s="3">
+        <v>-1.9077902058555001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>10</v>
       </c>
-      <c r="B5" t="n">
-        <v>-6.2344004288055</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-6.6213463242165</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-1.4479177985105</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1.7363584800405</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-1.452543733969</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-1.737719049293</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="B5" s="3">
+        <v>-6.2344004288055004</v>
+      </c>
+      <c r="C5" s="3">
+        <v>-6.6213463242164998</v>
+      </c>
+      <c r="D5" s="3">
+        <v>-1.4479177985105001</v>
+      </c>
+      <c r="E5" s="3">
+        <v>-1.7363584800405001</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-1.4525437339689999</v>
+      </c>
+      <c r="G5" s="3">
+        <v>-1.7377190492929999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>20</v>
       </c>
-      <c r="B6" t="n">
-        <v>-6.4809355773585</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-6.4003898776105</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="B6" s="3">
+        <v>-6.4809355773585002</v>
+      </c>
+      <c r="C6" s="3">
+        <v>-6.4003898776105004</v>
+      </c>
+      <c r="D6" s="3">
         <v>-1.7330931138345</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3">
         <v>-1.546150898541</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3">
         <v>-1.6737722944255</v>
       </c>
-      <c r="G6" t="n">
-        <v>-1.48574162373</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="G6" s="3">
+        <v>-1.4857416237300001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>30</v>
       </c>
-      <c r="B7" t="n">
-        <v>-6.4863778543685</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-6.448009801448</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-1.7537737664725</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.5698248035345</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="B7" s="3">
+        <v>-6.4863778543684996</v>
+      </c>
+      <c r="C7" s="3">
+        <v>-6.4480098014480003</v>
+      </c>
+      <c r="D7" s="3">
+        <v>-1.7537737664724999</v>
+      </c>
+      <c r="E7" s="3">
+        <v>-1.5698248035344999</v>
+      </c>
+      <c r="F7" s="3">
         <v>-1.683296279193</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3">
         <v>-1.497170405451</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>40</v>
       </c>
-      <c r="B8" t="n">
-        <v>-6.3944033728995</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-6.547603470731</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="B8" s="3">
+        <v>-6.3944033728995002</v>
+      </c>
+      <c r="C8" s="3">
+        <v>-6.5476034707309996</v>
+      </c>
+      <c r="D8" s="3">
         <v>-1.6051996040995</v>
       </c>
-      <c r="E8" t="n">
-        <v>-1.5937708223785</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="E8" s="3">
+        <v>-1.5937708223785001</v>
+      </c>
+      <c r="F8" s="3">
         <v>-1.6813914822395</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3">
         <v>-1.672411725173</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>50</v>
       </c>
-      <c r="B9" t="n">
-        <v>-6.5059700516045</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-6.467057770983001</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9" s="3">
+        <v>-6.5059700516044998</v>
+      </c>
+      <c r="C9" s="3">
+        <v>-6.4670577709830006</v>
+      </c>
+      <c r="D9" s="3">
         <v>-1.5785324467505</v>
       </c>
-      <c r="E9" t="n">
-        <v>-1.6296898506445</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9" s="3">
+        <v>-1.6296898506444999</v>
+      </c>
+      <c r="F9" s="3">
         <v>-1.6525474140865</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3">
         <v>-1.730099861479</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>60</v>
       </c>
-      <c r="B10" t="n">
-        <v>-6.6654287679975</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-6.32392588562</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-1.689282783904</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="B10" s="3">
+        <v>-6.6654287679974997</v>
+      </c>
+      <c r="C10" s="3">
+        <v>-6.3239258856199996</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-1.6892827839040001</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1.7564949049775</v>
       </c>
-      <c r="F10" t="n">
-        <v>-1.563021957272</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-1.6226148905315</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="F10" s="3">
+        <v>-1.5630219572720001</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-1.6226148905315001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>70</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="3">
         <v>-6.6632518571935</v>
       </c>
-      <c r="C11" t="n">
-        <v>-6.370185240205</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-1.7717332806055</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="C11" s="3">
+        <v>-6.3701852402050001</v>
+      </c>
+      <c r="D11" s="3">
+        <v>-1.7717332806054999</v>
+      </c>
+      <c r="E11" s="3">
         <v>-1.801937918011</v>
       </c>
-      <c r="F11" t="n">
-        <v>-1.5398922799795</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="F11" s="3">
+        <v>-1.5398922799795001</v>
+      </c>
+      <c r="G11" s="3">
         <v>-1.58914488692</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>80</v>
       </c>
-      <c r="B12" t="n">
-        <v>-6.554134203143</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-6.485833626667501</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-1.7167662828045</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="B12" s="3">
+        <v>-6.5541342031429997</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-6.4858336266675014</v>
+      </c>
+      <c r="D12" s="3">
+        <v>-1.7167662828045001</v>
+      </c>
+      <c r="E12" s="3">
         <v>-1.7554064495755</v>
       </c>
-      <c r="F12" t="n">
-        <v>-1.6100976534085</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1.647921478628</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="F12" s="3">
+        <v>-1.6100976534085001</v>
+      </c>
+      <c r="G12" s="3">
+        <v>-1.6479214786280001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>100</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="3">
         <v>-6.558488024751</v>
       </c>
-      <c r="C13" t="n">
-        <v>-6.530732412</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-1.6960856301665</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.7183989659075</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="C13" s="3">
+        <v>-6.5307324119999999</v>
+      </c>
+      <c r="D13" s="3">
+        <v>-1.6960856301664999</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-1.7183989659075001</v>
+      </c>
+      <c r="F13" s="3">
         <v>-1.689827011605</v>
       </c>
-      <c r="G13" t="n">
-        <v>-1.7069701841865</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="G13" s="3">
+        <v>-1.7069701841864999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>120</v>
       </c>
-      <c r="B14" t="n">
-        <v>-6.578080221987</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14" s="3">
+        <v>-6.5780802219870003</v>
+      </c>
+      <c r="C14" s="3">
         <v>-6.543793876824</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3">
         <v>-1.7314604307315</v>
       </c>
-      <c r="E14" t="n">
-        <v>-1.727378722974</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-1.7069701841865</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1.6998952240735</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="E14" s="3">
+        <v>-1.7273787229740001</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-1.7069701841864999</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-1.6998952240734999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>140</v>
       </c>
-      <c r="B15" t="n">
-        <v>-6.572093717276</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-6.5674677818175</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-1.7271066091235</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-1.7254739260205</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.7222085598145</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="B15" s="3">
+        <v>-6.5720937172760001</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-6.5674677818175002</v>
+      </c>
+      <c r="D15" s="3">
+        <v>-1.7271066091234999</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-1.7254739260205001</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-1.7222085598145001</v>
+      </c>
+      <c r="G15" s="3">
         <v>-1.7205758767115</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>160</v>
       </c>
-      <c r="B16" t="n">
-        <v>-6.569100464920501</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-6.568828351070001</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="B16" s="3">
+        <v>-6.5691004649205009</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-6.5688283510700014</v>
+      </c>
+      <c r="D16" s="3">
         <v>-1.7227527875155</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3">
         <v>-1.722480673665</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="3">
         <v>-1.722480673665</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3">
         <v>-1.722480673665</v>
       </c>
     </row>
@@ -815,5 +752,6 @@
     <mergeCell ref="D1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>